--- a/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
+++ b/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\GBRTE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0810523-4B82-4275-B69B-DF6216DAAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{C0810523-4B82-4275-B69B-DF6216DAAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94D499AC-DBAF-4FFD-ABF7-A656771F3B39}"/>
   <bookViews>
-    <workbookView xWindow="11775" yWindow="945" windowWidth="34050" windowHeight="22035" xr2:uid="{F5DFE386-DBEF-4AF1-963C-2CAABB7180AC}"/>
+    <workbookView xWindow="11775" yWindow="945" windowWidth="34050" windowHeight="22035" activeTab="2" xr2:uid="{F5DFE386-DBEF-4AF1-963C-2CAABB7180AC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="ESTRTE-grid-batteries" sheetId="2" r:id="rId2"/>
-    <sheet name="ESTRTE-pumped-hydro" sheetId="3" r:id="rId3"/>
+    <sheet name="Data" sheetId="4" r:id="rId2"/>
+    <sheet name="ESTRTE-grid-batteries" sheetId="2" r:id="rId3"/>
+    <sheet name="ESTRTE-pumped-hydro" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,30 +39,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>ESTRTE Electricity Storage Technology Round-Trip Efficiency</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>U.S. Energy Information Administration</t>
-  </si>
-  <si>
-    <t>Utility-scale batteries and pumped storage return about 80% of the electricity they store</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/todayinenergy/detail.php?id=46756</t>
+    <t>Central Electricity Authority, India, Ministry of Power</t>
+  </si>
+  <si>
+    <t>National Electricity Plan - Vol 1, Generation</t>
+  </si>
+  <si>
+    <t>https://cea.nic.in/wp-content/uploads/irp/2023/05/NEP_2022_32_FINAL_GAZETTE-1.pdf</t>
+  </si>
+  <si>
+    <t>Chapter 13, Pg.13.3 for Pumped storage round-trip efficiency and 13.4 (table 13.1) for battery Round-trip efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithium-Ion battery round-trip efficiency </t>
+  </si>
+  <si>
+    <t>(choosing middle value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source </t>
+  </si>
+  <si>
+    <t>National Electricity plan (for both images)</t>
+  </si>
+  <si>
+    <t>Pumped hydro round-trip efficiency</t>
   </si>
   <si>
     <t>Unit: dimensionless (% of stored electricity returned)</t>
   </si>
   <si>
+    <t>Grid batteries</t>
+  </si>
+  <si>
     <t>Round-trip efficiency</t>
-  </si>
-  <si>
-    <t>Grid batteries</t>
-  </si>
-  <si>
-    <t>ESTRTE Electricity Storage Technology Round-Trip Efficiency</t>
   </si>
   <si>
     <t>Pumped hydro</t>
@@ -71,7 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -135,6 +154,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -151,6 +173,102 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4737BBBA-D522-6D01-0769-126BABA16D55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="257175"/>
+          <a:ext cx="4572000" cy="2228850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27366238-4638-AC56-9EF8-E6744592E066}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4737BBBA-D522-6D01-0769-126BABA16D55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2857500"/>
+          <a:ext cx="4572000" cy="2390775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,35 +568,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EBD16E-FF3E-46B9-95CB-C7A74EFA7439}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="3">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -491,31 +614,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1FD866-B46A-4EAE-8DDF-C9A8CFF78045}">
+  <dimension ref="B1:C31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
+      <c r="B2" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9FA380-0802-4E12-9AD5-66B7BCF215AB}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>0.82</v>
+        <v>13</v>
+      </c>
+      <c r="B2" s="7">
+        <f>Data!B2</f>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -523,35 +689,210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB52EC4-0D58-482D-95ED-6F4A6D21B80A}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>0.79</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B2" s="7">
+        <f>Data!B31</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E26ABE9F-4AC6-4C6F-AACE-ABC90A1F66F1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D734D2DD-E2D5-4C10-BD64-118CF3AA3F17}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0E0ED2-2189-4057-AE63-F5EFE7F0706D}"/>
 </file>
--- a/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
+++ b/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
@@ -886,7 +886,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E26ABE9F-4AC6-4C6F-AACE-ABC90A1F66F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{332D01C9-1BCA-469E-9D96-2FE968EA42F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -894,5 +894,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0E0ED2-2189-4057-AE63-F5EFE7F0706D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E4771A8-887F-4A2F-8E7E-4B4E864675D8}"/>
 </file>